--- a/data/trans_orig/Q23_tabaco-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Edad media de inicio en el consumo de tabaco</t>
+          <t>Edad media de inicio en el consumo de tabaco (tasa de respuesta: 95,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,49; 16,03</t>
+          <t>15,48; 16,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,52 +726,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 16,14</t>
+          <t>15,42; 16,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 16,56</t>
+          <t>15,38; 16,52</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,52; 16,1</t>
+          <t>15,54; 16,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,02; 15,63</t>
+          <t>15,01; 15,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,88; 15,66</t>
+          <t>14,91; 15,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 16,46</t>
+          <t>15,46; 16,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,59; 16,01</t>
+          <t>15,59; 15,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 15,74</t>
+          <t>15,31; 15,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,32; 15,84</t>
+          <t>15,28; 15,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,53; 16,33</t>
+          <t>15,51; 16,32</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,74</t>
+          <t>16,26; 16,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 16,97</t>
+          <t>16,46; 16,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,88</t>
+          <t>16,34; 16,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,11; 17,29</t>
+          <t>16,12; 17,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,55; 17,17</t>
+          <t>16,57; 17,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 17,34</t>
+          <t>16,69; 17,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,49; 17,17</t>
+          <t>16,47; 17,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,42; 17,34</t>
+          <t>16,37; 17,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 16,83</t>
+          <t>16,48; 16,82</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,06</t>
+          <t>16,65; 17,05</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 16,93</t>
+          <t>16,47; 16,95</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,39; 17,18</t>
+          <t>16,4; 17,2</t>
         </is>
       </c>
     </row>
@@ -996,32 +996,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,41; 17,16</t>
+          <t>16,38; 17,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,16</t>
+          <t>16,49; 17,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 17,46</t>
+          <t>16,57; 17,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,44; 17,49</t>
+          <t>16,43; 17,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,81; 17,65</t>
+          <t>16,84; 17,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,9; 17,62</t>
+          <t>16,91; 17,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1031,27 +1031,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,85; 17,61</t>
+          <t>16,87; 17,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,68; 17,23</t>
+          <t>16,67; 17,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,25</t>
+          <t>16,78; 17,25</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,32</t>
+          <t>16,77; 17,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,36</t>
+          <t>16,76; 17,39</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,97; 16,55</t>
+          <t>15,95; 16,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 16,73</t>
+          <t>16,09; 16,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,1; 16,81</t>
+          <t>16,08; 16,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 17,63</t>
+          <t>16,21; 17,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,57; 18,73</t>
+          <t>17,58; 18,86</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,53</t>
+          <t>17,41; 18,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 18,13</t>
+          <t>17,33; 18,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,15; 17,88</t>
+          <t>17,18; 17,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,23</t>
+          <t>16,65; 17,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,74; 17,33</t>
+          <t>16,71; 17,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,73; 17,28</t>
+          <t>16,77; 17,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,37; 17,55</t>
+          <t>16,46; 17,58</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1276,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,91; 16,8</t>
+          <t>15,9; 16,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,18; 17,22</t>
+          <t>16,18; 17,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1291,22 +1291,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,11; 16,74</t>
+          <t>16,12; 16,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,09; 23,97</t>
+          <t>20,16; 23,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 21,4</t>
+          <t>19,03; 21,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,02</t>
+          <t>18,73; 21,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1316,22 +1316,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,01</t>
+          <t>16,91; 18,1</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 18,18</t>
+          <t>17,11; 18,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 18,27</t>
+          <t>17,14; 18,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,62; 17,13</t>
+          <t>16,6; 17,11</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,05; 17,65</t>
+          <t>16,01; 17,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,84; 16,95</t>
+          <t>15,85; 16,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,93; 17,17</t>
+          <t>15,96; 17,23</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,97; 16,7</t>
+          <t>15,98; 16,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,12; 30,47</t>
+          <t>21,16; 30,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,93; 35,25</t>
+          <t>23,66; 34,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20,97; 26,01</t>
+          <t>21,0; 25,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,38; 20,48</t>
+          <t>18,41; 20,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,82; 18,67</t>
+          <t>16,81; 18,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,98; 18,93</t>
+          <t>16,89; 18,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,85</t>
+          <t>17,27; 18,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,8; 17,6</t>
+          <t>16,82; 17,64</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 16,73</t>
+          <t>15,19; 16,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 16,97</t>
+          <t>15,71; 16,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,6; 17,77</t>
+          <t>15,53; 17,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,96; 17,0</t>
+          <t>16,03; 17,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,03; 36,07</t>
+          <t>15,89; 36,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,61; 37,4</t>
+          <t>22,75; 36,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,96; 23,06</t>
+          <t>18,81; 23,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 24,77</t>
+          <t>18,45; 25,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,59; 17,97</t>
+          <t>15,51; 17,93</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,28; 18,08</t>
+          <t>16,29; 18,17</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 17,92</t>
+          <t>15,93; 17,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,49; 17,72</t>
+          <t>16,48; 17,73</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,22; 16,53</t>
+          <t>16,22; 16,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,36; 16,66</t>
+          <t>16,34; 16,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,33; 16,7</t>
+          <t>16,32; 16,68</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,3; 16,76</t>
+          <t>16,31; 16,78</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,25; 17,81</t>
+          <t>17,22; 17,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,99</t>
+          <t>17,42; 18,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,43; 17,97</t>
+          <t>17,42; 17,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,28; 17,69</t>
+          <t>17,27; 17,7</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,94</t>
+          <t>16,65; 16,93</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,12</t>
+          <t>16,83; 17,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,14</t>
+          <t>16,84; 17,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,66; 17,05</t>
+          <t>16,63; 17,06</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q23_tabaco-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q23_tabaco-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15,91</t>
+          <t>15,97</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>15,96</t>
+          <t>16,11</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,94</t>
+          <t>16,04</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,48; 16,02</t>
+          <t>15,48; 16,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,47; 16,01</t>
+          <t>15,45; 16,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,42; 16,12</t>
+          <t>15,41; 16,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,38; 16,52</t>
+          <t>15,44; 16,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,54; 16,13</t>
+          <t>15,53; 16,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,01; 15,66</t>
+          <t>14,99; 15,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,91; 15,64</t>
+          <t>14,92; 15,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,46; 16,43</t>
+          <t>15,57; 16,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15,59; 15,99</t>
+          <t>15,6; 15,99</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,31; 15,73</t>
+          <t>15,33; 15,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 15,8</t>
+          <t>15,28; 15,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,51; 16,32</t>
+          <t>15,63; 16,36</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,71</t>
+          <t>16,68</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>16,86</t>
+          <t>16,91</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,78</t>
+          <t>16,79</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,26; 16,71</t>
+          <t>16,28; 16,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>16,46; 16,97</t>
+          <t>16,44; 16,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,9</t>
+          <t>16,3; 16,89</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,12; 17,37</t>
+          <t>16,14; 17,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,17</t>
+          <t>16,54; 17,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 17,32</t>
+          <t>16,71; 17,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 17,16</t>
+          <t>16,48; 17,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,37; 17,37</t>
+          <t>16,46; 17,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16,48; 16,82</t>
+          <t>16,46; 16,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,05</t>
+          <t>16,64; 17,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16,47; 16,95</t>
+          <t>16,46; 16,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,4; 17,2</t>
+          <t>16,44; 17,13</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>16,89</t>
+          <t>16,91</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,17</t>
+          <t>17,16</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 17,18</t>
+          <t>16,36; 17,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,49; 17,12</t>
+          <t>16,49; 17,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,57; 17,44</t>
+          <t>16,57; 17,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 17,49</t>
+          <t>16,48; 17,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,66</t>
+          <t>16,8; 17,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,91; 17,62</t>
+          <t>16,94; 17,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,43</t>
+          <t>16,78; 17,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16,87; 17,6</t>
+          <t>16,86; 17,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,67; 17,2</t>
+          <t>16,67; 17,22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,78; 17,25</t>
+          <t>16,77; 17,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,31</t>
+          <t>16,74; 17,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,76; 17,39</t>
+          <t>16,78; 17,33</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16,77</t>
+          <t>17,39</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,48</t>
+          <t>17,61</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,0</t>
+          <t>17,49</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,95; 16,54</t>
+          <t>15,98; 16,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 16,74</t>
+          <t>16,09; 16,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16,08; 16,8</t>
+          <t>16,11; 16,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,21; 17,59</t>
+          <t>16,97; 18,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,58; 18,86</t>
+          <t>17,6; 18,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,33; 18,13</t>
+          <t>17,32; 18,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,18; 17,92</t>
+          <t>17,25; 18,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,65; 17,26</t>
+          <t>16,68; 17,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16,71; 17,35</t>
+          <t>16,74; 17,35</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16,77; 17,29</t>
+          <t>16,74; 17,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,46; 17,58</t>
+          <t>17,21; 17,86</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,41</t>
+          <t>16,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>17,69</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>17,42</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>17,61</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>17,42</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>17,61</t>
-        </is>
-      </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
           <t>17,64</t>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,87</t>
+          <t>16,96</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>15,9; 16,8</t>
+          <t>15,91; 16,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,18; 17,17</t>
+          <t>16,17; 17,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,93; 16,88</t>
+          <t>15,91; 16,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,12; 16,69</t>
+          <t>16,2; 16,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,16; 23,97</t>
+          <t>20,15; 23,98</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,03; 21,4</t>
+          <t>18,91; 21,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,01</t>
+          <t>18,69; 20,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,26; 18,05</t>
+          <t>17,31; 18,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16,91; 18,1</t>
+          <t>16,85; 18,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 18,16</t>
+          <t>17,17; 18,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,14; 18,28</t>
+          <t>17,17; 18,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,6; 17,11</t>
+          <t>16,71; 17,24</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16,33</t>
+          <t>16,46</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19,25</t>
+          <t>19,21</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,19</t>
+          <t>17,26</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 17,66</t>
+          <t>16,03; 17,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15,85; 16,9</t>
+          <t>15,81; 16,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,96; 17,23</t>
+          <t>15,95; 17,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,98; 16,69</t>
+          <t>16,08; 16,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,16; 30,58</t>
+          <t>21,26; 30,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>23,66; 34,91</t>
+          <t>23,94; 34,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,0; 25,56</t>
+          <t>20,95; 25,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,41; 20,41</t>
+          <t>18,42; 20,47</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,81; 18,68</t>
+          <t>16,78; 18,56</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,89; 18,92</t>
+          <t>16,94; 18,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17,27; 18,86</t>
+          <t>17,31; 18,98</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16,82; 17,64</t>
+          <t>16,87; 17,75</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16,44</t>
+          <t>16,43</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>20,2</t>
+          <t>20,36</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,97</t>
+          <t>17,0</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,19; 16,8</t>
+          <t>15,19; 16,71</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,71; 16,97</t>
+          <t>15,67; 17,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,53; 17,73</t>
+          <t>15,56; 17,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,03; 17,01</t>
+          <t>15,98; 17,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,89; 36,42</t>
+          <t>15,78; 35,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,75; 36,5</t>
+          <t>22,16; 36,27</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 23,06</t>
+          <t>18,82; 23,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 25,37</t>
+          <t>18,63; 24,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>15,51; 17,93</t>
+          <t>15,53; 18,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16,29; 18,17</t>
+          <t>16,26; 18,36</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,93; 17,97</t>
+          <t>15,85; 17,85</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16,48; 17,73</t>
+          <t>16,5; 17,69</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16,57</t>
+          <t>16,71</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>17,46</t>
+          <t>17,53</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>16,9</t>
+          <t>17,04</t>
         </is>
       </c>
     </row>
@@ -1701,57 +1701,57 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16,34; 16,66</t>
+          <t>16,36; 16,65</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,32; 16,68</t>
+          <t>16,31; 16,67</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>16,31; 16,78</t>
+          <t>16,54; 16,91</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>17,22; 17,8</t>
+          <t>17,26; 17,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,42; 18,0</t>
+          <t>17,42; 17,98</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,42; 17,94</t>
+          <t>17,43; 17,95</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>17,27; 17,7</t>
+          <t>17,33; 17,76</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>16,65; 16,93</t>
+          <t>16,66; 16,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16,83; 17,11</t>
+          <t>16,84; 17,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16,84; 17,14</t>
+          <t>16,82; 17,14</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,63; 17,06</t>
+          <t>16,93; 17,18</t>
         </is>
       </c>
     </row>
